--- a/dcf/LITE.xlsx
+++ b/dcf/LITE.xlsx
@@ -432,7 +432,7 @@
     </comment>
     <comment ref="B45" authorId="0" shapeId="0">
       <text>
-        <t>Opus: 14.0x</t>
+        <t>User-edited — overridden from Opus 14.0x</t>
       </text>
     </comment>
     <comment ref="B46" authorId="0" shapeId="0">
@@ -1128,184 +1128,184 @@
     </row>
     <row r="5">
       <c r="A5" s="53" t="n">
-        <v>11</v>
+        <v>11.2</v>
       </c>
       <c r="B5" s="54" t="n">
-        <v>298.0752431679612</v>
+        <v>301.7793437300527</v>
       </c>
       <c r="C5" s="54" t="n">
-        <v>287.3217101935289</v>
+        <v>290.8620243891975</v>
       </c>
       <c r="D5" s="54" t="n">
-        <v>277.0690172819782</v>
+        <v>280.4534763859012</v>
       </c>
       <c r="E5" s="54" t="n">
-        <v>267.2914008296996</v>
+        <v>270.5275189755603</v>
       </c>
       <c r="F5" s="54" t="n">
-        <v>257.9645379924577</v>
+        <v>261.0594358364658</v>
       </c>
       <c r="G5" s="54" t="n">
-        <v>249.0654599203189</v>
+        <v>252.0258868653916</v>
       </c>
       <c r="H5" s="54" t="n">
-        <v>240.5724705813437</v>
+        <v>243.4048256553411</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="53" t="n">
-        <v>12</v>
+        <v>12.2</v>
       </c>
       <c r="B6" s="54" t="n">
-        <v>316.5957459784188</v>
+        <v>320.2998465405104</v>
       </c>
       <c r="C6" s="54" t="n">
-        <v>305.0232811718718</v>
+        <v>308.5635953675403</v>
       </c>
       <c r="D6" s="54" t="n">
-        <v>293.9913128015933</v>
+        <v>297.3757719055163</v>
       </c>
       <c r="E6" s="54" t="n">
-        <v>283.471991559003</v>
+        <v>286.7081097048636</v>
       </c>
       <c r="F6" s="54" t="n">
-        <v>273.4390272124982</v>
+        <v>276.5339250565063</v>
       </c>
       <c r="G6" s="54" t="n">
-        <v>263.8675946456826</v>
+        <v>266.8280215907553</v>
       </c>
       <c r="H6" s="54" t="n">
-        <v>254.7342459513309</v>
+        <v>257.5666010253283</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="53" t="n">
-        <v>13</v>
+        <v>13.2</v>
       </c>
       <c r="B7" s="54" t="n">
-        <v>335.1162487888764</v>
+        <v>338.8203493509679</v>
       </c>
       <c r="C7" s="54" t="n">
-        <v>322.7248521502145</v>
+        <v>326.2651663458831</v>
       </c>
       <c r="D7" s="54" t="n">
-        <v>310.9136083212084</v>
+        <v>314.2980674251314</v>
       </c>
       <c r="E7" s="54" t="n">
-        <v>299.6525822883063</v>
+        <v>302.8887004341669</v>
       </c>
       <c r="F7" s="54" t="n">
-        <v>288.9135164325387</v>
+        <v>292.0084142765468</v>
       </c>
       <c r="G7" s="54" t="n">
-        <v>278.6697293710463</v>
+        <v>281.630156316119</v>
       </c>
       <c r="H7" s="54" t="n">
-        <v>268.8960213213182</v>
+        <v>271.7283763953156</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="53" t="n">
-        <v>14</v>
+        <v>14.2</v>
       </c>
       <c r="B8" s="54" t="n">
-        <v>353.6367515993341</v>
+        <v>357.3408521614256</v>
       </c>
       <c r="C8" s="54" t="n">
-        <v>340.4264231285574</v>
+        <v>343.966737324226</v>
       </c>
       <c r="D8" s="54" t="n">
-        <v>327.8359038408235</v>
+        <v>331.2203629447465</v>
       </c>
       <c r="E8" s="55" t="n">
-        <v>315.8331730176097</v>
+        <v>319.0692911634703</v>
       </c>
       <c r="F8" s="54" t="n">
-        <v>304.3880056525792</v>
+        <v>307.4829034965873</v>
       </c>
       <c r="G8" s="54" t="n">
-        <v>293.47186409641</v>
+        <v>296.4322910414827</v>
       </c>
       <c r="H8" s="54" t="n">
-        <v>283.0577966913055</v>
+        <v>285.8901517653028</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="53" t="n">
-        <v>15</v>
+        <v>15.2</v>
       </c>
       <c r="B9" s="54" t="n">
-        <v>372.1572544097917</v>
+        <v>375.8613549718832</v>
       </c>
       <c r="C9" s="54" t="n">
-        <v>358.1279941069002</v>
+        <v>361.6683083025688</v>
       </c>
       <c r="D9" s="54" t="n">
-        <v>344.7581993604386</v>
+        <v>348.1426584643617</v>
       </c>
       <c r="E9" s="54" t="n">
-        <v>332.013763746913</v>
+        <v>335.2498818927737</v>
       </c>
       <c r="F9" s="54" t="n">
-        <v>319.8624948726197</v>
+        <v>322.9573927166278</v>
       </c>
       <c r="G9" s="54" t="n">
-        <v>308.2739988217737</v>
+        <v>311.2344257668464</v>
       </c>
       <c r="H9" s="54" t="n">
-        <v>297.2195720612927</v>
+        <v>300.0519271352902</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="53" t="n">
-        <v>16</v>
+        <v>16.2</v>
       </c>
       <c r="B10" s="54" t="n">
-        <v>390.6777572202494</v>
+        <v>394.3818577823408</v>
       </c>
       <c r="C10" s="54" t="n">
-        <v>375.8295650852431</v>
+        <v>379.3698792809116</v>
       </c>
       <c r="D10" s="54" t="n">
-        <v>361.6804948800537</v>
+        <v>365.0649539839767</v>
       </c>
       <c r="E10" s="54" t="n">
-        <v>348.1943544762165</v>
+        <v>351.4304726220771</v>
       </c>
       <c r="F10" s="54" t="n">
-        <v>335.3369840926602</v>
+        <v>338.4318819366683</v>
       </c>
       <c r="G10" s="54" t="n">
-        <v>323.0761335471374</v>
+        <v>326.0365604922101</v>
       </c>
       <c r="H10" s="54" t="n">
-        <v>311.3813474312799</v>
+        <v>314.2137025052774</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="53" t="n">
-        <v>17</v>
+        <v>17.2</v>
       </c>
       <c r="B11" s="54" t="n">
-        <v>409.198260030707</v>
+        <v>412.9023605927985</v>
       </c>
       <c r="C11" s="54" t="n">
-        <v>393.531136063586</v>
+        <v>397.0714502592544</v>
       </c>
       <c r="D11" s="54" t="n">
-        <v>378.6027903996689</v>
+        <v>381.9872495035918</v>
       </c>
       <c r="E11" s="54" t="n">
-        <v>364.3749452055199</v>
+        <v>367.6110633513805</v>
       </c>
       <c r="F11" s="54" t="n">
-        <v>350.8114733127008</v>
+        <v>353.9063711567089</v>
       </c>
       <c r="G11" s="54" t="n">
-        <v>337.8782682725011</v>
+        <v>340.8386952175739</v>
       </c>
       <c r="H11" s="54" t="n">
-        <v>325.5431228012673</v>
+        <v>328.3754778752646</v>
       </c>
     </row>
     <row r="13">
@@ -1328,7 +1328,7 @@
         <v>0.1180853982292283</v>
       </c>
       <c r="C14" s="57" t="n">
-        <v>14</v>
+        <v>14.2</v>
       </c>
     </row>
   </sheetData>
@@ -1671,7 +1671,7 @@
         </is>
       </c>
       <c r="I8" s="49" t="n">
-        <v>0.9544847480135671</v>
+        <v>0.9531962764666105</v>
       </c>
       <c r="K8" s="25">
         <f>MAX(-0.05,NORMINV(RAND(),$C$6,$D$6))</f>
@@ -24375,7 +24375,7 @@
         </is>
       </c>
       <c r="B45" s="19" t="n">
-        <v>14</v>
+        <v>14.2</v>
       </c>
     </row>
     <row r="46">
@@ -24572,13 +24572,13 @@
         </is>
       </c>
       <c r="B58" s="28" t="n">
-        <v>315.8331730176097</v>
+        <v>319.0692911634703</v>
       </c>
       <c r="C58" s="28" t="n">
-        <v>423.4580372442818</v>
+        <v>427.460778517013</v>
       </c>
       <c r="D58" s="28" t="n">
-        <v>233.4876354425097</v>
+        <v>236.0882403916614</v>
       </c>
     </row>
     <row r="59">
@@ -25174,9 +25174,9 @@
         <f>Dashboard!B45</f>
         <v/>
       </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Opus</t>
+      <c r="D32" s="32" t="inlineStr">
+        <is>
+          <t>user-edited</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -25184,7 +25184,11 @@
           <t>14.0x</t>
         </is>
       </c>
-      <c r="F32" s="31" t="inlineStr"/>
+      <c r="F32" s="31" t="inlineStr">
+        <is>
+          <t>overridden from Opus 14.0x</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">

--- a/dcf/LITE.xlsx
+++ b/dcf/LITE.xlsx
@@ -849,7 +849,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
     </row>
@@ -1105,25 +1105,25 @@
         </is>
       </c>
       <c r="B4" s="52" t="n">
-        <v>0.1030853982292283</v>
+        <v>0.1030835198190921</v>
       </c>
       <c r="C4" s="52" t="n">
-        <v>0.1080853982292283</v>
+        <v>0.1080835198190921</v>
       </c>
       <c r="D4" s="52" t="n">
-        <v>0.1130853982292283</v>
+        <v>0.1130835198190921</v>
       </c>
       <c r="E4" s="52" t="n">
-        <v>0.1180853982292283</v>
+        <v>0.1180835198190921</v>
       </c>
       <c r="F4" s="52" t="n">
-        <v>0.1230853982292283</v>
+        <v>0.1230835198190921</v>
       </c>
       <c r="G4" s="52" t="n">
-        <v>0.1280853982292283</v>
+        <v>0.1280835198190921</v>
       </c>
       <c r="H4" s="52" t="n">
-        <v>0.1330853982292283</v>
+        <v>0.1330835198190921</v>
       </c>
     </row>
     <row r="5">
@@ -1131,25 +1131,25 @@
         <v>11.2</v>
       </c>
       <c r="B5" s="54" t="n">
-        <v>301.7793437300527</v>
+        <v>202.6094316017639</v>
       </c>
       <c r="C5" s="54" t="n">
-        <v>290.8620243891975</v>
+        <v>195.8997095304377</v>
       </c>
       <c r="D5" s="54" t="n">
-        <v>280.4534763859012</v>
+        <v>189.4997570262236</v>
       </c>
       <c r="E5" s="54" t="n">
-        <v>270.5275189755603</v>
+        <v>183.3937021410956</v>
       </c>
       <c r="F5" s="54" t="n">
-        <v>261.0594358364658</v>
+        <v>177.5665586829631</v>
       </c>
       <c r="G5" s="54" t="n">
-        <v>252.0258868653916</v>
+        <v>172.0041729380759</v>
       </c>
       <c r="H5" s="54" t="n">
-        <v>243.4048256553411</v>
+        <v>166.6931738226099</v>
       </c>
     </row>
     <row r="6">
@@ -1157,25 +1157,25 @@
         <v>12.2</v>
       </c>
       <c r="B6" s="54" t="n">
-        <v>320.2998465405104</v>
+        <v>213.7566957028582</v>
       </c>
       <c r="C6" s="54" t="n">
-        <v>308.5635953675403</v>
+        <v>206.554067760191</v>
       </c>
       <c r="D6" s="54" t="n">
-        <v>297.3757719055163</v>
+        <v>199.6850781498171</v>
       </c>
       <c r="E6" s="54" t="n">
-        <v>286.7081097048636</v>
+        <v>193.1325995571728</v>
       </c>
       <c r="F6" s="54" t="n">
-        <v>276.5339250565063</v>
+        <v>186.8804616380189</v>
       </c>
       <c r="G6" s="54" t="n">
-        <v>266.8280215907553</v>
+        <v>180.9133934092034</v>
       </c>
       <c r="H6" s="54" t="n">
-        <v>257.5666010253283</v>
+        <v>175.2169693496751</v>
       </c>
     </row>
     <row r="7">
@@ -1183,25 +1183,25 @@
         <v>13.2</v>
       </c>
       <c r="B7" s="54" t="n">
-        <v>338.8203493509679</v>
+        <v>224.9039598039524</v>
       </c>
       <c r="C7" s="54" t="n">
-        <v>326.2651663458831</v>
+        <v>217.2084259899443</v>
       </c>
       <c r="D7" s="54" t="n">
-        <v>314.2980674251314</v>
+        <v>209.8703992734106</v>
       </c>
       <c r="E7" s="54" t="n">
-        <v>302.8887004341669</v>
+        <v>202.8714969732501</v>
       </c>
       <c r="F7" s="54" t="n">
-        <v>292.0084142765468</v>
+        <v>196.1943645930746</v>
       </c>
       <c r="G7" s="54" t="n">
-        <v>281.630156316119</v>
+        <v>189.8226138803309</v>
       </c>
       <c r="H7" s="54" t="n">
-        <v>271.7283763953156</v>
+        <v>183.7407648767402</v>
       </c>
     </row>
     <row r="8">
@@ -1209,25 +1209,25 @@
         <v>14.2</v>
       </c>
       <c r="B8" s="54" t="n">
-        <v>357.3408521614256</v>
+        <v>236.0512239050466</v>
       </c>
       <c r="C8" s="54" t="n">
-        <v>343.966737324226</v>
+        <v>227.8627842196976</v>
       </c>
       <c r="D8" s="54" t="n">
-        <v>331.2203629447465</v>
+        <v>220.0557203970041</v>
       </c>
       <c r="E8" s="55" t="n">
-        <v>319.0692911634703</v>
+        <v>212.6103943893274</v>
       </c>
       <c r="F8" s="54" t="n">
-        <v>307.4829034965873</v>
+        <v>205.5082675481304</v>
       </c>
       <c r="G8" s="54" t="n">
-        <v>296.4322910414827</v>
+        <v>198.7318343514585</v>
       </c>
       <c r="H8" s="54" t="n">
-        <v>285.8901517653028</v>
+        <v>192.2645604038053</v>
       </c>
     </row>
     <row r="9">
@@ -1235,25 +1235,25 @@
         <v>15.2</v>
       </c>
       <c r="B9" s="54" t="n">
-        <v>375.8613549718832</v>
+        <v>247.1984880061408</v>
       </c>
       <c r="C9" s="54" t="n">
-        <v>361.6683083025688</v>
+        <v>238.5171424494509</v>
       </c>
       <c r="D9" s="54" t="n">
-        <v>348.1426584643617</v>
+        <v>230.2410415205976</v>
       </c>
       <c r="E9" s="54" t="n">
-        <v>335.2498818927737</v>
+        <v>222.3492918054046</v>
       </c>
       <c r="F9" s="54" t="n">
-        <v>322.9573927166278</v>
+        <v>214.8221705031862</v>
       </c>
       <c r="G9" s="54" t="n">
-        <v>311.2344257668464</v>
+        <v>207.641054822586</v>
       </c>
       <c r="H9" s="54" t="n">
-        <v>300.0519271352902</v>
+        <v>200.7883559308704</v>
       </c>
     </row>
     <row r="10">
@@ -1261,25 +1261,25 @@
         <v>16.2</v>
       </c>
       <c r="B10" s="54" t="n">
-        <v>394.3818577823408</v>
+        <v>258.3457521072351</v>
       </c>
       <c r="C10" s="54" t="n">
-        <v>379.3698792809116</v>
+        <v>249.1715006792042</v>
       </c>
       <c r="D10" s="54" t="n">
-        <v>365.0649539839767</v>
+        <v>240.4263626441911</v>
       </c>
       <c r="E10" s="54" t="n">
-        <v>351.4304726220771</v>
+        <v>232.0881892214818</v>
       </c>
       <c r="F10" s="54" t="n">
-        <v>338.4318819366683</v>
+        <v>224.136073458242</v>
       </c>
       <c r="G10" s="54" t="n">
-        <v>326.0365604922101</v>
+        <v>216.5502752937135</v>
       </c>
       <c r="H10" s="54" t="n">
-        <v>314.2137025052774</v>
+        <v>209.3121514579356</v>
       </c>
     </row>
     <row r="11">
@@ -1287,25 +1287,25 @@
         <v>17.2</v>
       </c>
       <c r="B11" s="54" t="n">
-        <v>412.9023605927985</v>
+        <v>269.4930162083293</v>
       </c>
       <c r="C11" s="54" t="n">
-        <v>397.0714502592544</v>
+        <v>259.8258589089576</v>
       </c>
       <c r="D11" s="54" t="n">
-        <v>381.9872495035918</v>
+        <v>250.6116837677846</v>
       </c>
       <c r="E11" s="54" t="n">
-        <v>367.6110633513805</v>
+        <v>241.8270866375591</v>
       </c>
       <c r="F11" s="54" t="n">
-        <v>353.9063711567089</v>
+        <v>233.4499764132977</v>
       </c>
       <c r="G11" s="54" t="n">
-        <v>340.8386952175739</v>
+        <v>225.459495764841</v>
       </c>
       <c r="H11" s="54" t="n">
-        <v>328.3754778752646</v>
+        <v>217.8359469850007</v>
       </c>
     </row>
     <row r="13">
@@ -1315,7 +1315,7 @@
         </is>
       </c>
       <c r="B13" s="54" t="n">
-        <v>728.3200073242188</v>
+        <v>702.3775024414062</v>
       </c>
     </row>
     <row r="14">
@@ -1325,7 +1325,7 @@
         </is>
       </c>
       <c r="B14" s="56" t="n">
-        <v>0.1180853982292283</v>
+        <v>0.1180835198190921</v>
       </c>
       <c r="C14" s="57" t="n">
         <v>14.2</v>
@@ -1671,7 +1671,7 @@
         </is>
       </c>
       <c r="I8" s="49" t="n">
-        <v>0.9531962764666105</v>
+        <v>0.9849328480812229</v>
       </c>
       <c r="K8" s="25">
         <f>MAX(-0.05,NORMINV(RAND(),$C$6,$D$6))</f>
@@ -24410,7 +24410,7 @@
         </is>
       </c>
       <c r="B48" s="23" t="n">
-        <v>728.3200073242188</v>
+        <v>702.3775024414062</v>
       </c>
     </row>
     <row r="49">
@@ -24420,7 +24420,7 @@
         </is>
       </c>
       <c r="B49" s="20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -24572,13 +24572,13 @@
         </is>
       </c>
       <c r="B58" s="28" t="n">
-        <v>319.0692911634703</v>
+        <v>212.6103943893274</v>
       </c>
       <c r="C58" s="28" t="n">
-        <v>427.460778517013</v>
+        <v>275.5452206554479</v>
       </c>
       <c r="D58" s="28" t="n">
-        <v>236.0882403916614</v>
+        <v>163.3327980804023</v>
       </c>
     </row>
     <row r="59">
